--- a/KontrolniSignali.xlsx
+++ b/KontrolniSignali.xlsx
@@ -1,40 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\.Cloud Documents\Osman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6841F18F-B1E5-4C45-B956-90BB512431E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E18F754-00C0-4FC5-8723-893D2AA455AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{09ED3171-E7C3-41A1-AF7D-6506862602DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="KontrolniSignali" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="90">
   <si>
     <t>Instr</t>
   </si>
@@ -205,6 +197,105 @@
   </si>
   <si>
     <t>MemIzv</t>
+  </si>
+  <si>
+    <t>MOV</t>
+  </si>
+  <si>
+    <t>00000000000000000</t>
+  </si>
+  <si>
+    <t>00000000010001000</t>
+  </si>
+  <si>
+    <t>00000000011001000</t>
+  </si>
+  <si>
+    <t>00000000001001000</t>
+  </si>
+  <si>
+    <t>00000000100001000</t>
+  </si>
+  <si>
+    <t>00000000101001000</t>
+  </si>
+  <si>
+    <t>00000000110001000</t>
+  </si>
+  <si>
+    <t>00000001000001000</t>
+  </si>
+  <si>
+    <t>00000001001001000</t>
+  </si>
+  <si>
+    <t>00000000010011000</t>
+  </si>
+  <si>
+    <t>00000000011011000</t>
+  </si>
+  <si>
+    <t>00000000100011000</t>
+  </si>
+  <si>
+    <t>00000000101011000</t>
+  </si>
+  <si>
+    <t>00000000110011000</t>
+  </si>
+  <si>
+    <t>11100000000011100</t>
+  </si>
+  <si>
+    <t>00010000000000000</t>
+  </si>
+  <si>
+    <t>00000100000011011</t>
+  </si>
+  <si>
+    <t>00000010000010011</t>
+  </si>
+  <si>
+    <t>00000000111011000</t>
+  </si>
+  <si>
+    <t>11100000000010000</t>
+  </si>
+  <si>
+    <t>00100000000010000</t>
+  </si>
+  <si>
+    <t>01000000000010000</t>
+  </si>
+  <si>
+    <t>01100000000010000</t>
+  </si>
+  <si>
+    <t>10000000000010000</t>
+  </si>
+  <si>
+    <t>10100000000010000</t>
+  </si>
+  <si>
+    <t>11000000000010000</t>
+  </si>
+  <si>
+    <t>00000100010101010</t>
+  </si>
+  <si>
+    <t>00000010010100010</t>
+  </si>
+  <si>
+    <t>00000000010101000</t>
+  </si>
+  <si>
+    <t>00001000011000000</t>
+  </si>
+  <si>
+    <t>00001000011010000</t>
+  </si>
+  <si>
+    <t>00000000111001000</t>
   </si>
 </sst>
 </file>
@@ -257,7 +348,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -326,11 +417,67 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -384,6 +531,57 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -700,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A312F852-CFA9-4CEE-A43B-C5028C909E4E}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="15" max="15" width="20" customWidth="1"/>
@@ -845,7 +1043,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="str">
-        <f t="shared" ref="O3:O32" si="0">_xlfn.TEXTJOIN("", TRUE, TEXT(C3,"000"), D3:G3, TEXT(H3, "0000"), I3:K3, TEXT(L3, "00"), M3)</f>
+        <f t="shared" ref="O3:Q33" si="0">_xlfn.TEXTJOIN("", TRUE, TEXT(C3,"000"), D3:G3, TEXT(H3, "0000"), I3:K3, TEXT(L3, "00"), M3)</f>
         <v>00000000010001000</v>
       </c>
     </row>
@@ -2146,46 +2344,46 @@
       </c>
     </row>
     <row r="31" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="11">
-        <v>0</v>
-      </c>
-      <c r="D31" s="6">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6">
-        <v>1</v>
-      </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-      <c r="G31" s="6">
-        <v>0</v>
-      </c>
-      <c r="H31" s="8" t="s">
+      <c r="C31" s="21">
+        <v>0</v>
+      </c>
+      <c r="D31" s="22">
+        <v>0</v>
+      </c>
+      <c r="E31" s="22">
+        <v>1</v>
+      </c>
+      <c r="F31" s="22">
+        <v>0</v>
+      </c>
+      <c r="G31" s="22">
+        <v>0</v>
+      </c>
+      <c r="H31" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="I31" s="6">
-        <v>0</v>
-      </c>
-      <c r="J31" s="6">
-        <v>0</v>
-      </c>
-      <c r="K31" s="6">
-        <v>0</v>
-      </c>
-      <c r="L31" s="12">
-        <v>0</v>
-      </c>
-      <c r="M31" s="18">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3">
+      <c r="I31" s="22">
+        <v>0</v>
+      </c>
+      <c r="J31" s="22">
+        <v>0</v>
+      </c>
+      <c r="K31" s="22">
+        <v>0</v>
+      </c>
+      <c r="L31" s="24">
+        <v>0</v>
+      </c>
+      <c r="M31" s="25">
+        <v>0</v>
+      </c>
+      <c r="N31" s="19">
         <v>11101</v>
       </c>
       <c r="O31" t="str">
@@ -2194,55 +2392,277 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="11">
-        <v>0</v>
-      </c>
-      <c r="D32" s="6">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6">
-        <v>1</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0</v>
-      </c>
-      <c r="G32" s="6">
-        <v>0</v>
-      </c>
-      <c r="H32" s="8" t="s">
+      <c r="C32" s="28">
+        <v>0</v>
+      </c>
+      <c r="D32" s="29">
+        <v>0</v>
+      </c>
+      <c r="E32" s="29">
+        <v>1</v>
+      </c>
+      <c r="F32" s="29">
+        <v>0</v>
+      </c>
+      <c r="G32" s="29">
+        <v>0</v>
+      </c>
+      <c r="H32" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="I32" s="6">
-        <v>0</v>
-      </c>
-      <c r="J32" s="6">
-        <v>1</v>
-      </c>
-      <c r="K32" s="6">
-        <v>0</v>
-      </c>
-      <c r="L32" s="12">
-        <v>0</v>
-      </c>
-      <c r="M32" s="18">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="I32" s="29">
+        <v>0</v>
+      </c>
+      <c r="J32" s="29">
+        <v>1</v>
+      </c>
+      <c r="K32" s="29">
+        <v>0</v>
+      </c>
+      <c r="L32" s="30">
+        <v>0</v>
+      </c>
+      <c r="M32" s="31">
+        <v>0</v>
+      </c>
+      <c r="N32" s="32">
         <v>11110</v>
       </c>
       <c r="O32" t="str">
         <f t="shared" si="0"/>
         <v>00001000011010000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="28">
+        <v>0</v>
+      </c>
+      <c r="D33" s="34">
+        <v>0</v>
+      </c>
+      <c r="E33" s="34">
+        <v>0</v>
+      </c>
+      <c r="F33" s="34">
+        <v>0</v>
+      </c>
+      <c r="G33" s="34">
+        <v>0</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="I33" s="34">
+        <v>0</v>
+      </c>
+      <c r="J33" s="34">
+        <v>0</v>
+      </c>
+      <c r="K33" s="34">
+        <v>1</v>
+      </c>
+      <c r="L33" s="30">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34">
+        <v>0</v>
+      </c>
+      <c r="N33" s="32">
+        <v>11111</v>
+      </c>
+      <c r="O33" t="str">
+        <f t="shared" si="0"/>
+        <v>00000000111001000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5320DE7C-CFB8-4847-A8F0-F80B28E51DA1}">
+  <dimension ref="A1:A32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>